--- a/job_application_forms/039_tech_industry_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/039_tech_industry_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -903,8 +903,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -932,12 +932,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'html/css'}</t>
+          <t>html/css</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'HTML/CSS'}</t>
+          <t>HTML/CSS</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'python'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Python'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'more_than_1_year'}</t>
+          <t>more_than_1_year</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'More than 1 year'}</t>
+          <t>More than 1 year</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
